--- a/latest/BoM/Generic/pedalboard-display-bom.xlsx
+++ b/latest/BoM/Generic/pedalboard-display-bom.xlsx
@@ -217,7 +217,7 @@
     <t>KiCad Version:</t>
   </si>
   <si>
-    <t>8.0.6+1</t>
+    <t>9.0.1</t>
   </si>
   <si>
     <t>Component Groups:</t>
@@ -447,10 +447,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>3186525</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>297815</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1464384</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>123779</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -477,7 +477,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9396825" cy="5079365"/>
+          <a:ext cx="2378784" cy="1285829"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -499,10 +499,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>3024600</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>107315</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>16584</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>123779</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -529,7 +529,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="9396825" cy="5079365"/>
+          <a:ext cx="2378784" cy="1285829"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
